--- a/grammar-basicTerms/Grammar-基本詞彙.xlsx
+++ b/grammar-basicTerms/Grammar-基本詞彙.xlsx
@@ -15063,15 +15063,15 @@
     <t>sunguc</t>
   </si>
   <si>
+    <t>Seediq_A2-17-63.mp3</t>
+  </si>
+  <si>
+    <t>sunan</t>
+  </si>
+  <si>
     <t>Seediq_A2-17-62.mp3</t>
   </si>
   <si>
-    <t>sunan</t>
-  </si>
-  <si>
-    <t>Seediq_A2-17-63.mp3</t>
-  </si>
-  <si>
     <t>supih</t>
   </si>
   <si>
@@ -15243,7 +15243,7 @@
     <t>Seediq_A2-18-22.mp3</t>
   </si>
   <si>
-    <t>tmapaq</t>
+    <t>tmapaq baga</t>
   </si>
   <si>
     <t>拍擊；摑掌</t>
@@ -44235,7 +44235,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="4" t="s">
+      <c r="A611" s="5" t="s">
         <v>5076</v>
       </c>
       <c r="B611" s="4" t="s">
